--- a/data/rag.xlsx
+++ b/data/rag.xlsx
@@ -509,25 +509,25 @@
     <t>3см плотность 30 кг - 1200р/м2</t>
   </si>
   <si>
-    <t>3см плотность 30 кг ППУ</t>
-  </si>
-  <si>
-    <t>5см плотность 30 кг ППУ</t>
-  </si>
-  <si>
     <t>5см плотность 30 кг - 1400р/м2</t>
   </si>
   <si>
-    <t>7см плотность 30 кг ППУ</t>
-  </si>
-  <si>
     <t>7см плотность 30 кг - 1800р/м2</t>
   </si>
   <si>
-    <t>10см плотность 20 кг ППУ</t>
-  </si>
-  <si>
     <t>10см плотность 20 кг - 2100р/м2</t>
+  </si>
+  <si>
+    <t>цена 3см плотность 30 кг ППУ</t>
+  </si>
+  <si>
+    <t>цена 5см плотность 30 кг ППУ</t>
+  </si>
+  <si>
+    <t>цена 7см плотность 30 кг ППУ</t>
+  </si>
+  <si>
+    <t>цена 10см плотность 20 кг ППУ</t>
   </si>
 </sst>
 </file>
@@ -855,7 +855,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>155</v>
@@ -866,10 +866,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>154</v>
@@ -877,10 +877,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>154</v>
@@ -888,10 +888,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>154</v>

--- a/data/rag.xlsx
+++ b/data/rag.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Сообщения" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Сообщения!$A$1:$C$80</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Сообщения!$A$1:$C$81</definedName>
   </definedNames>
   <calcPr calcId="145621"/>
   <extLst>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="166">
   <si>
     <t>с чердака пенят паропроницаемой пеной толщиной 10 см и более</t>
   </si>
@@ -320,9 +320,6 @@
     <t>чем лучше подшить потолок в мансарде доской или осб</t>
   </si>
   <si>
-    <t>по поводу открытой ячейки. Она получается пропускает пар и может в ней копиться конденсат зимой? Нужно изнутри дома закрывать пароизоляцией пену?</t>
-  </si>
-  <si>
     <t>мансарда конденсат</t>
   </si>
   <si>
@@ -344,12 +341,6 @@
     <t>скидка</t>
   </si>
   <si>
-    <t>Дорого выходит в сравнение с минеральной ватой.</t>
-  </si>
-  <si>
-    <t>дорого</t>
-  </si>
-  <si>
     <t>пол деревянный, если подполье низкое, и не будет ли гнить дерево?</t>
   </si>
   <si>
@@ -528,6 +519,24 @@
   </si>
   <si>
     <t>цена 10см плотность 20 кг ППУ</t>
+  </si>
+  <si>
+    <t>Возражение Дорого выходит в сравнение с минеральной ватой.</t>
+  </si>
+  <si>
+    <t>Возражение дорого</t>
+  </si>
+  <si>
+    <t>мансарда ППУ с открытой ячейки. Она получается пропускает пар и может в ней копиться конденсат зимой? Нужно изнутри дома закрывать пароизоляцией пену?</t>
+  </si>
+  <si>
+    <t>Пароизоляция, ветрозащита нужна</t>
+  </si>
+  <si>
+    <t>Для ППУ пароизоляция Не нужна, это лишнее, различные плёнки приводят к удорожанию утепления. ППУ прекрасно пропускает пар, без образования сырости</t>
+  </si>
+  <si>
+    <t>Пароизоляция</t>
   </si>
 </sst>
 </file>
@@ -812,7 +821,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C80"/>
+  <dimension ref="A1:C81"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="48.85546875" customWidth="1"/>
@@ -822,10 +831,10 @@
   <sheetData>
     <row r="1" spans="1:3" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>72</v>
@@ -833,13 +842,13 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -855,46 +864,46 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="150" x14ac:dyDescent="0.25">
@@ -943,7 +952,7 @@
     </row>
     <row r="12" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>79</v>
@@ -1069,313 +1078,313 @@
     </row>
     <row r="24" spans="1:3" ht="105" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>93</v>
+        <v>162</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A26" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="B26" s="1"/>
+      <c r="C26" s="4" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+      <c r="A27" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="B25" s="1"/>
-      <c r="C25" s="4" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" ht="60" x14ac:dyDescent="0.25">
-      <c r="A26" s="4" t="s">
+      <c r="B27" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C27" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="B26" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C26" s="4" t="s">
+    </row>
+    <row r="28" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A28" s="4" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="27" spans="1:3" ht="45" x14ac:dyDescent="0.25">
-      <c r="A27" s="4" t="s">
+      <c r="B28" s="1"/>
+      <c r="C28" s="4" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A29" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C29" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="B27" s="1"/>
-      <c r="C27" s="4" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A28" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C28" s="4" t="s">
+    </row>
+    <row r="30" spans="1:3" ht="135" x14ac:dyDescent="0.25">
+      <c r="A30" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A32" s="4" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="29" spans="1:3" ht="135" x14ac:dyDescent="0.25">
-      <c r="A29" s="4" t="s">
+      <c r="B32" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C32" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="B29" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="C29" s="4" t="s">
+    </row>
+    <row r="33" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A33" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C33" s="4" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A31" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C31" s="4" t="s">
+    <row r="34" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A34" s="4" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="32" spans="1:3" ht="45" x14ac:dyDescent="0.25">
-      <c r="A32" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A33" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="B33" s="1" t="s">
+      <c r="B34" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C33" s="4" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
+      <c r="C34" s="4" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="B34" s="4" t="s">
+      <c r="B35" s="4" t="s">
         <v>16</v>
-      </c>
-      <c r="C34" s="4" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="B35" s="4" t="s">
-        <v>108</v>
       </c>
       <c r="C35" s="4" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>68</v>
+      <c r="A36" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>105</v>
       </c>
       <c r="C36" s="4" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" s="4" t="s">
+      <c r="A37" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A39" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="C39" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="B37" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="C37" s="4" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" ht="45" x14ac:dyDescent="0.25">
-      <c r="A38" s="4" t="s">
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="B38" s="4" t="s">
+      <c r="B40" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A41" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="C38" s="4" t="s">
+      <c r="B41" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A42" s="4" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" s="4" t="s">
+      <c r="B42" s="1"/>
+      <c r="C42" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="B39" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C39" s="4" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A40" s="4" t="s">
+    </row>
+    <row r="43" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C43" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="B40" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="C40" s="4" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" ht="45" x14ac:dyDescent="0.25">
-      <c r="A41" s="4" t="s">
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="B41" s="1"/>
-      <c r="C41" s="4" t="s">
+      <c r="B44" s="1"/>
+      <c r="C44" s="4" t="s">
         <v>117</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C42" s="4" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="B43" s="1"/>
-      <c r="C43" s="4" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C44" s="4" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B45" s="1" t="s">
+      <c r="B46" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C45" s="4" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A46" s="1" t="s">
+      <c r="C46" s="4" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B46" s="1"/>
-      <c r="C46" s="4" t="s">
+      <c r="B47" s="1"/>
+      <c r="C47" s="4" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47" s="1" t="s">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B47" s="1" t="s">
+      <c r="B48" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C47" s="4" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" ht="45" x14ac:dyDescent="0.25">
-      <c r="A48" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="B48" s="1"/>
       <c r="C48" s="4" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B49" s="1"/>
       <c r="C49" s="4" t="s">
-        <v>126</v>
+        <v>76</v>
       </c>
     </row>
     <row r="50" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="B50" s="1"/>
       <c r="C50" s="4" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="B51" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B51" s="1"/>
+      <c r="C51" s="4" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="B52" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C51" s="4" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" ht="45" x14ac:dyDescent="0.25">
-      <c r="A52" s="1" t="s">
+      <c r="C52" s="4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B52" s="1" t="s">
+      <c r="B53" s="1" t="s">
         <v>64</v>
-      </c>
-      <c r="C52" s="4" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A53" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="B53" s="4" t="s">
-        <v>130</v>
       </c>
       <c r="C53" s="4" t="s">
         <v>90</v>
@@ -1383,186 +1392,186 @@
     </row>
     <row r="54" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A55" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C56" s="4" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" ht="75" x14ac:dyDescent="0.25">
+      <c r="A57" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B57" s="1"/>
+      <c r="C57" s="4" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A58" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="C58" s="4" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" ht="240" x14ac:dyDescent="0.25">
+      <c r="A59" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B59" s="1"/>
+      <c r="C59" s="4" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+      <c r="A60" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="B54" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C54" s="4" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A55" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C55" s="4" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" ht="75" x14ac:dyDescent="0.25">
-      <c r="A56" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B56" s="1"/>
-      <c r="C56" s="4" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A57" s="4" t="s">
+      <c r="B60" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A61" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A62" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C62" s="4" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" ht="105" x14ac:dyDescent="0.25">
+      <c r="A63" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="B57" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="C57" s="4" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" ht="240" x14ac:dyDescent="0.25">
-      <c r="A58" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B58" s="1"/>
-      <c r="C58" s="4" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" ht="60" x14ac:dyDescent="0.25">
-      <c r="A59" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C59" s="4" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A60" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C60" s="4" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" ht="45" x14ac:dyDescent="0.25">
-      <c r="A61" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C61" s="4" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" ht="105" x14ac:dyDescent="0.25">
-      <c r="A62" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="B62" s="1" t="s">
+      <c r="B63" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C62" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A63" s="1"/>
-      <c r="B63" s="1"/>
       <c r="C63" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" ht="45" x14ac:dyDescent="0.25">
-      <c r="A64" s="4" t="s">
-        <v>135</v>
-      </c>
+        <v>97</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" s="1"/>
       <c r="B64" s="1"/>
       <c r="C64" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="65" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="B65" s="1"/>
+      <c r="C65" s="4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A66" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="B66" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="C66" s="4" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A67" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B67" s="1"/>
+      <c r="C67" s="4" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+      <c r="A68" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C68" s="4" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B69" s="1"/>
+      <c r="C69" s="4" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A70" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="B65" s="4" t="s">
+      <c r="B70" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C70" s="4" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B71" s="1"/>
+      <c r="C71" s="4" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A72" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B72" s="4" t="s">
         <v>138</v>
-      </c>
-      <c r="C65" s="4" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A66" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B66" s="1"/>
-      <c r="C66" s="4" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" ht="60" x14ac:dyDescent="0.25">
-      <c r="A67" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C67" s="4" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B68" s="1"/>
-      <c r="C68" s="4" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A69" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C69" s="4" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B70" s="1"/>
-      <c r="C70" s="4" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" ht="45" x14ac:dyDescent="0.25">
-      <c r="A71" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B71" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="C71" s="4" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A72" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="B72" s="4" t="s">
-        <v>143</v>
       </c>
       <c r="C72" s="4" t="s">
         <v>90</v>
@@ -1570,86 +1579,97 @@
     </row>
     <row r="73" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A73" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="B73" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="C73" s="4" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A74" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C74" s="4" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A75" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C75" s="4" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B76" s="1"/>
+      <c r="C76" s="4" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A77" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C77" s="4" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A78" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B78" s="1"/>
+      <c r="C78" s="4" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="B79" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="C79" s="4" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A80" s="4" t="s">
         <v>144</v>
-      </c>
-      <c r="B73" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C73" s="4" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A74" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B74" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C74" s="4" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A75" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B75" s="1"/>
-      <c r="C75" s="4" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A76" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B76" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C76" s="4" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3" ht="45" x14ac:dyDescent="0.25">
-      <c r="A77" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B77" s="1"/>
-      <c r="C77" s="4" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A78" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="B78" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="C78" s="4" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3" ht="45" x14ac:dyDescent="0.25">
-      <c r="A79" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="B79" s="1"/>
-      <c r="C79" s="4" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A80" s="4" t="s">
-        <v>148</v>
       </c>
       <c r="B80" s="1"/>
       <c r="C80" s="4" t="s">
         <v>90</v>
       </c>
     </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="B81" s="1"/>
+      <c r="C81" s="4" t="s">
+        <v>90</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:C80"/>
+  <autoFilter ref="A1:C81"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape" r:id="rId1"/>
 </worksheet>

--- a/data/rag.xlsx
+++ b/data/rag.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Сообщения" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Сообщения!$A$1:$C$81</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Сообщения!$A$1:$C$82</definedName>
   </definedNames>
   <calcPr calcId="145621"/>
   <extLst>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="168">
   <si>
     <t>с чердака пенят паропроницаемой пеной толщиной 10 см и более</t>
   </si>
@@ -509,18 +509,9 @@
     <t>10см плотность 20 кг - 2100р/м2</t>
   </si>
   <si>
-    <t>цена 3см плотность 30 кг ППУ</t>
-  </si>
-  <si>
     <t>цена 5см плотность 30 кг ППУ</t>
   </si>
   <si>
-    <t>цена 7см плотность 30 кг ППУ</t>
-  </si>
-  <si>
-    <t>цена 10см плотность 20 кг ППУ</t>
-  </si>
-  <si>
     <t>Возражение Дорого выходит в сравнение с минеральной ватой.</t>
   </si>
   <si>
@@ -537,6 +528,21 @@
   </si>
   <si>
     <t>Пароизоляция</t>
+  </si>
+  <si>
+    <t>Сколько стоит выезд для утепления</t>
+  </si>
+  <si>
+    <t>цена утепления ППУ пеноблока, бетона, кирпича, арболита, керамзитоблока, бруса, бревна</t>
+  </si>
+  <si>
+    <t>цена утепления ППУ мансарда</t>
+  </si>
+  <si>
+    <t>цена утепления ППУ каркасник, каркасные стены, пол, потолок</t>
+  </si>
+  <si>
+    <t>По поселку Игра бесплатно, в другие места по 15 за км. В случае проведения утепления, эта сумма входит в сумму утепления, т.е. выезд будет бесплатно</t>
   </si>
 </sst>
 </file>
@@ -821,7 +827,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C81"/>
+  <dimension ref="A1:C82"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="48.85546875" customWidth="1"/>
@@ -862,9 +868,9 @@
         <v>73</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>152</v>
@@ -875,7 +881,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>153</v>
@@ -886,7 +892,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>154</v>
@@ -895,9 +901,9 @@
         <v>151</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>155</v>
@@ -1078,7 +1084,7 @@
     </row>
     <row r="24" spans="1:3" ht="105" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>28</v>
@@ -1089,13 +1095,13 @@
     </row>
     <row r="25" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="30" x14ac:dyDescent="0.25">
@@ -1140,13 +1146,13 @@
     </row>
     <row r="30" spans="1:3" ht="135" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>69</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
@@ -1668,8 +1674,19 @@
         <v>90</v>
       </c>
     </row>
+    <row r="82" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>163</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="C82" s="4" t="s">
+        <v>76</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:C81"/>
+  <autoFilter ref="A1:C82"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape" r:id="rId1"/>
 </worksheet>

--- a/data/rag.xlsx
+++ b/data/rag.xlsx
@@ -533,16 +533,16 @@
     <t>Сколько стоит выезд для утепления</t>
   </si>
   <si>
-    <t>цена утепления ППУ пеноблока, бетона, кирпича, арболита, керамзитоблока, бруса, бревна</t>
-  </si>
-  <si>
-    <t>цена утепления ППУ мансарда</t>
-  </si>
-  <si>
-    <t>цена утепления ППУ каркасник, каркасные стены, пол, потолок</t>
-  </si>
-  <si>
     <t>По поселку Игра бесплатно, в другие места по 15 за км. В случае проведения утепления, эта сумма входит в сумму утепления, т.е. выезд будет бесплатно</t>
+  </si>
+  <si>
+    <t>цена 3см плотность 30 кг ППУ</t>
+  </si>
+  <si>
+    <t>цена 7см плотность 30 кг ППУ</t>
+  </si>
+  <si>
+    <t>цена 10см плотность 20 кг ППУ</t>
   </si>
 </sst>
 </file>
@@ -827,6 +827,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:C82"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -846,7 +847,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>149</v>
       </c>
@@ -857,7 +858,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>71</v>
       </c>
@@ -868,9 +869,9 @@
         <v>73</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>152</v>
@@ -892,7 +893,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>154</v>
@@ -901,9 +902,9 @@
         <v>151</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>155</v>
@@ -912,7 +913,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="150" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" ht="150" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>9</v>
       </c>
@@ -923,7 +924,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>74</v>
       </c>
@@ -934,7 +935,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>3</v>
       </c>
@@ -945,7 +946,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="285" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" ht="285" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>2</v>
       </c>
@@ -956,7 +957,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
         <v>150</v>
       </c>
@@ -967,7 +968,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
         <v>80</v>
       </c>
@@ -978,7 +979,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
         <v>82</v>
       </c>
@@ -989,7 +990,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>44</v>
       </c>
@@ -998,7 +999,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
         <v>84</v>
       </c>
@@ -1009,7 +1010,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>40</v>
       </c>
@@ -1020,7 +1021,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>56</v>
       </c>
@@ -1031,7 +1032,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>58</v>
       </c>
@@ -1042,7 +1043,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
         <v>89</v>
       </c>
@@ -1053,7 +1054,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
         <v>12</v>
       </c>
@@ -1064,7 +1065,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
         <v>91</v>
       </c>
@@ -1073,7 +1074,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
         <v>92</v>
       </c>
@@ -1082,7 +1083,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="105" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" ht="105" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
         <v>159</v>
       </c>
@@ -1093,7 +1094,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>160</v>
       </c>
@@ -1104,7 +1105,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
         <v>95</v>
       </c>
@@ -1113,7 +1114,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
         <v>96</v>
       </c>
@@ -1124,7 +1125,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
         <v>98</v>
       </c>
@@ -1133,7 +1134,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
         <v>42</v>
       </c>
@@ -1144,7 +1145,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="135" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" ht="135" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
         <v>157</v>
       </c>
@@ -1155,7 +1156,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>37</v>
       </c>
@@ -1166,7 +1167,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
         <v>100</v>
       </c>
@@ -1177,7 +1178,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
         <v>103</v>
       </c>
@@ -1188,7 +1189,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
         <v>104</v>
       </c>
@@ -1199,7 +1200,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>66</v>
       </c>
@@ -1210,7 +1211,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
         <v>106</v>
       </c>
@@ -1221,7 +1222,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>67</v>
       </c>
@@ -1232,7 +1233,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
         <v>107</v>
       </c>
@@ -1243,7 +1244,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
         <v>108</v>
       </c>
@@ -1254,7 +1255,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
         <v>111</v>
       </c>
@@ -1265,7 +1266,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
         <v>112</v>
       </c>
@@ -1276,7 +1277,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
         <v>113</v>
       </c>
@@ -1285,7 +1286,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>14</v>
       </c>
@@ -1296,7 +1297,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
         <v>116</v>
       </c>
@@ -1305,7 +1306,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>27</v>
       </c>
@@ -1316,7 +1317,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>32</v>
       </c>
@@ -1327,7 +1328,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>34</v>
       </c>
@@ -1336,7 +1337,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>35</v>
       </c>
@@ -1347,7 +1348,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="49" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
         <v>121</v>
       </c>
@@ -1356,7 +1357,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="50" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
         <v>122</v>
       </c>
@@ -1365,7 +1366,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="51" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
         <v>124</v>
       </c>
@@ -1374,7 +1375,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
         <v>125</v>
       </c>
@@ -1385,7 +1386,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="53" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>63</v>
       </c>
@@ -1396,7 +1397,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="54" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:3" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
         <v>126</v>
       </c>
@@ -1407,7 +1408,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="55" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:3" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
         <v>128</v>
       </c>
@@ -1418,7 +1419,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="56" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:3" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>30</v>
       </c>
@@ -1429,7 +1430,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="57" spans="1:3" ht="75" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:3" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>39</v>
       </c>
@@ -1438,7 +1439,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="58" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:3" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
         <v>130</v>
       </c>
@@ -1449,7 +1450,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="59" spans="1:3" ht="240" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:3" ht="240" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>25</v>
       </c>
@@ -1458,7 +1459,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="60" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:3" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
         <v>131</v>
       </c>
@@ -1469,7 +1470,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="61" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:3" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>19</v>
       </c>
@@ -1480,7 +1481,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="62" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:3" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>21</v>
       </c>
@@ -1491,7 +1492,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="63" spans="1:3" ht="105" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:3" ht="105" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" s="4" t="s">
         <v>133</v>
       </c>
@@ -1502,14 +1503,14 @@
         <v>97</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" s="1"/>
       <c r="B64" s="1"/>
       <c r="C64" s="4" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="65" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:3" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
         <v>132</v>
       </c>
@@ -1518,7 +1519,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="66" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:3" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
         <v>134</v>
       </c>
@@ -1529,7 +1530,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="67" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:3" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>50</v>
       </c>
@@ -1538,7 +1539,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="68" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:3" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
         <v>136</v>
       </c>
@@ -1549,13 +1550,13 @@
         <v>90</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="B69" s="1"/>
       <c r="C69" s="4" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="70" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:3" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
         <v>137</v>
       </c>
@@ -1566,13 +1567,13 @@
         <v>90</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="B71" s="1"/>
       <c r="C71" s="4" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="72" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:3" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>53</v>
       </c>
@@ -1583,7 +1584,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="73" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:3" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" s="4" t="s">
         <v>139</v>
       </c>
@@ -1594,7 +1595,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="74" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:3" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
         <v>141</v>
       </c>
@@ -1605,7 +1606,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="75" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:3" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
         <v>60</v>
       </c>
@@ -1616,7 +1617,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
         <v>62</v>
       </c>
@@ -1625,7 +1626,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="77" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:3" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
         <v>48</v>
       </c>
@@ -1636,7 +1637,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="78" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:3" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
         <v>26</v>
       </c>
@@ -1645,7 +1646,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" s="4" t="s">
         <v>143</v>
       </c>
@@ -1656,7 +1657,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="80" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:3" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
         <v>144</v>
       </c>
@@ -1665,7 +1666,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" s="4" t="s">
         <v>145</v>
       </c>
@@ -1674,19 +1675,25 @@
         <v>90</v>
       </c>
     </row>
-    <row r="82" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:3" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>163</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C82" s="4" t="s">
         <v>76</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C82"/>
+  <autoFilter ref="A1:C82">
+    <filterColumn colId="2">
+      <filters>
+        <filter val="цена"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape" r:id="rId1"/>
 </worksheet>

--- a/data/rag.xlsx
+++ b/data/rag.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="174">
   <si>
     <t>с чердака пенят паропроницаемой пеной толщиной 10 см и более</t>
   </si>
@@ -188,9 +188,6 @@
     <t>Можно, но чтобы строго небыло в составе никаких масляных и нефтяных эмульсий ...</t>
   </si>
   <si>
-    <t>Толщина 5см,   плотность материала 30кг</t>
-  </si>
-  <si>
     <t>Мин заказ в м²?</t>
   </si>
   <si>
@@ -489,25 +486,10 @@
     <t>2100р/м2</t>
   </si>
   <si>
-    <t>цена утепления ППУ кирпич</t>
-  </si>
-  <si>
-    <t>цена утепления ППУ пеноблок, газоблок, брус, бревно, арболит, шлакоблок, керамзитоблок</t>
-  </si>
-  <si>
-    <t>цена утепления ППУ каркасные стены, потолок, пол</t>
-  </si>
-  <si>
-    <t>цена утепления ППУ мансарда</t>
-  </si>
-  <si>
     <t>толщина</t>
   </si>
   <si>
     <t>толщина 3см или 5 см. возможен вариант сплошного покрытия или эконом утепления - это заливка только швов между бревнами, плотность пены 30 кг</t>
-  </si>
-  <si>
-    <t>толщина утепления пенополиуретаном для мансарды</t>
   </si>
   <si>
     <t>видео утепления стен из пеноблока</t>
@@ -530,21 +512,6 @@
 2) плотность материала 20кг,  толщина 10-13см</t>
   </si>
   <si>
-    <t>толщина утепления пенополиуретаном для стен из пеноблока</t>
-  </si>
-  <si>
-    <t>толщина утепления пенополиуретаном для стен из бревна</t>
-  </si>
-  <si>
-    <t>толщина утепления пенополиуретаном для стен из бруса</t>
-  </si>
-  <si>
-    <t>толщина 3см или 5 см. плотность пены 30 кг</t>
-  </si>
-  <si>
-    <t>толщина утепления пенополиуретаном для стен из арболита</t>
-  </si>
-  <si>
     <t>Толщина 3 см плотность 30 кг</t>
   </si>
   <si>
@@ -552,13 +519,159 @@
   </si>
   <si>
     <t xml:space="preserve">нужен осмотр  вашего специалиста. </t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">толщина утепления ППУ для </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>{</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF001080"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>object_type</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA31515"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> из </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>{</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF001080"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>material</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>}</t>
+    </r>
+  </si>
+  <si>
+    <t>толщина утепления ППУ для стен из бревна</t>
+  </si>
+  <si>
+    <t>толщина утепления ППУ для стен из арболита</t>
+  </si>
+  <si>
+    <t>толщина утепления ППУ для стен из бруса</t>
+  </si>
+  <si>
+    <t>толщина утепления ППУ для мансарды</t>
+  </si>
+  <si>
+    <t>толщина утепления ППУ для стен из пеноблока</t>
+  </si>
+  <si>
+    <t>Шаблон строки поиска по базе</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">цена утепления ППУ толщина </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>{</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF001080"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>thickness</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>} плотность</t>
+    </r>
+  </si>
+  <si>
+    <t>цена утепления ППУ толщина 3 см плотность 30 кг</t>
+  </si>
+  <si>
+    <t>цена утепления ППУ толщина 5 см  плотность 30 кг</t>
+  </si>
+  <si>
+    <t>цена утепления ППУ толщина 7 см  плотность 30 кг</t>
+  </si>
+  <si>
+    <t>толщина 3см или 5 см. плотность 30 кг</t>
+  </si>
+  <si>
+    <t>Толщина 5см,   плотность 30кг</t>
+  </si>
+  <si>
+    <t>цена утепления ППУ толщина 10 см  плотность 20 кг</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -577,14 +690,6 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="16"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="204"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -606,6 +711,45 @@
       <name val="Courier New"/>
       <family val="3"/>
       <charset val="204"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFA31515"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF001080"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -634,7 +778,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -642,24 +786,28 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -873,186 +1021,196 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:C83"/>
+  <dimension ref="A1:D83"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="48.85546875" style="10" customWidth="1"/>
+    <col min="1" max="1" width="48.85546875" style="8" customWidth="1"/>
     <col min="2" max="2" width="100.5703125" customWidth="1"/>
     <col min="3" max="3" width="29.140625" customWidth="1"/>
+    <col min="4" max="4" width="54.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="21" x14ac:dyDescent="0.35">
-      <c r="A1" s="7" t="s">
-        <v>134</v>
-      </c>
-      <c r="B1" s="3" t="s">
+    <row r="1" spans="1:4" ht="21" x14ac:dyDescent="0.35">
+      <c r="A1" s="10" t="s">
         <v>133</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="D1" s="12" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="4" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
-        <v>65</v>
+      <c r="C2" s="3" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>64</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="30" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>151</v>
+      <c r="C3" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>168</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="C4" s="4" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="B5" s="2" t="s">
+      <c r="C5" s="3" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="C5" s="4" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="3" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="C6" s="4" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="30" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="150" hidden="1" x14ac:dyDescent="0.25">
+      <c r="C7" s="3" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="150" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="45" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
         <v>67</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="45" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>68</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="4" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="C9" s="3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="4" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="285" hidden="1" x14ac:dyDescent="0.25">
+      <c r="C10" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="285" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C11" s="4" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="30" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="45" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
+      <c r="C11" s="3" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A12" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="45" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B13" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="B13" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="30" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="8" t="s">
-        <v>167</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="30" hidden="1" x14ac:dyDescent="0.25">
+      <c r="C13" s="3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A14" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>40</v>
       </c>
       <c r="B15" s="1"/>
-      <c r="C15" s="4" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
-        <v>75</v>
+      <c r="C15" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
+        <v>74</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C16" s="4" t="s">
-        <v>76</v>
+      <c r="C16" s="3" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="17" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
@@ -1062,143 +1220,143 @@
       <c r="B17" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C17" s="4" t="s">
-        <v>77</v>
+      <c r="C17" s="3" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="18" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B18" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>77</v>
+      <c r="C18" s="3" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="19" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B19" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C19" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="C19" s="4" t="s">
+    </row>
+    <row r="20" spans="1:3" ht="30" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
         <v>79</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="30" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="4" t="s">
-        <v>80</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C20" s="4" t="s">
-        <v>81</v>
+      <c r="C20" s="3" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="60" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="4" t="s">
+      <c r="A21" s="3" t="s">
         <v>10</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="C21" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="30" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" ht="30" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="4" t="s">
+      <c r="B22" s="3"/>
+      <c r="C22" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="30" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="B22" s="4"/>
-      <c r="C22" s="4" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="30" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="4" t="s">
-        <v>83</v>
-      </c>
       <c r="B23" s="1"/>
-      <c r="C23" s="4" t="s">
-        <v>81</v>
+      <c r="C23" s="3" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="105" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="4" t="s">
-        <v>140</v>
+      <c r="A24" s="3" t="s">
+        <v>139</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C24" s="4" t="s">
+      <c r="C24" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="30" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="30" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B26" s="1"/>
+      <c r="C26" s="3" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="30" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" ht="30" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="4" t="s">
+    <row r="27" spans="1:3" ht="60" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="B26" s="1"/>
-      <c r="C26" s="4" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" ht="60" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="4" t="s">
+      <c r="B27" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C27" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="B27" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C27" s="4" t="s">
+    </row>
+    <row r="28" spans="1:3" ht="45" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="3" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="28" spans="1:3" ht="45" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="4" t="s">
-        <v>89</v>
-      </c>
       <c r="B28" s="1"/>
-      <c r="C28" s="4" t="s">
-        <v>85</v>
+      <c r="C28" s="3" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="30" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="4" t="s">
+      <c r="A29" s="3" t="s">
         <v>38</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C29" s="4" t="s">
-        <v>90</v>
+      <c r="C29" s="3" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="135" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="4" t="s">
+      <c r="A30" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C30" s="3" t="s">
         <v>138</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="31" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
@@ -1208,116 +1366,116 @@
       <c r="B31" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C31" s="4" t="s">
-        <v>85</v>
+      <c r="C31" s="3" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="30" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="4" t="s">
-        <v>91</v>
+      <c r="A32" s="3" t="s">
+        <v>90</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C32" s="4" t="s">
-        <v>92</v>
+      <c r="C32" s="3" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="45" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="4" t="s">
-        <v>94</v>
+      <c r="A33" s="3" t="s">
+        <v>93</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C33" s="4" t="s">
-        <v>93</v>
+      <c r="C33" s="3" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="30" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="4" t="s">
-        <v>95</v>
+      <c r="A34" s="3" t="s">
+        <v>94</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="4" t="s">
-        <v>93</v>
+      <c r="C34" s="3" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B35" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B35" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C35" s="4" t="s">
-        <v>69</v>
+      <c r="C35" s="3" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="36" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="B36" s="4" t="s">
+      <c r="A36" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="C36" s="4" t="s">
-        <v>69</v>
+      <c r="B36" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="37" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B37" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B37" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="C37" s="4" t="s">
-        <v>69</v>
+      <c r="C37" s="3" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="45" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="4" t="s">
+      <c r="A38" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B38" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="B38" s="4" t="s">
+      <c r="C38" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="C38" s="4" t="s">
+    </row>
+    <row r="39" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A39" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" ht="30" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="3" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="39" spans="1:3" ht="30" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="8" t="s">
-        <v>165</v>
-      </c>
-      <c r="B39" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="C39" s="4" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" ht="30" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="4" t="s">
+      <c r="B40" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" ht="45" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="B40" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C40" s="4" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" ht="45" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="4" t="s">
+      <c r="B41" s="1"/>
+      <c r="C41" s="3" t="s">
         <v>102</v>
-      </c>
-      <c r="B41" s="1"/>
-      <c r="C41" s="4" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="30" hidden="1" x14ac:dyDescent="0.25">
@@ -1327,17 +1485,17 @@
       <c r="B42" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C42" s="4" t="s">
+      <c r="C42" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="3" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="43" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="4" t="s">
+      <c r="B43" s="1"/>
+      <c r="C43" s="3" t="s">
         <v>105</v>
-      </c>
-      <c r="B43" s="1"/>
-      <c r="C43" s="4" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="44" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
@@ -1347,8 +1505,8 @@
       <c r="B44" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C44" s="4" t="s">
-        <v>107</v>
+      <c r="C44" s="3" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="45" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
@@ -1358,8 +1516,8 @@
       <c r="B45" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C45" s="4" t="s">
-        <v>108</v>
+      <c r="C45" s="3" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="46" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
@@ -1369,79 +1527,79 @@
       <c r="B46" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C46" s="4" t="s">
+      <c r="C46" s="3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="B47" s="1"/>
+      <c r="C47" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" ht="30" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="3" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="B47" s="1"/>
-      <c r="C47" s="4" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" ht="30" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="4" t="s">
+      <c r="B48" s="1"/>
+      <c r="C48" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="B48" s="1"/>
-      <c r="C48" s="4" t="s">
+    </row>
+    <row r="49" spans="1:3" ht="30" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="3" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="49" spans="1:3" ht="30" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="4" t="s">
+      <c r="B49" s="1"/>
+      <c r="C49" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="3" t="s">
         <v>112</v>
-      </c>
-      <c r="B49" s="1"/>
-      <c r="C49" s="4" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="4" t="s">
-        <v>113</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C50" s="4" t="s">
-        <v>92</v>
+      <c r="C50" s="3" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="51" spans="1:3" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B51" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B51" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C51" s="4" t="s">
-        <v>81</v>
+      <c r="C51" s="3" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="52" spans="1:3" ht="30" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="4" t="s">
+      <c r="A52" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="B52" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="B52" s="4" t="s">
+      <c r="C52" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A53" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="C52" s="4" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" ht="30" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="C53" s="4" t="s">
-        <v>154</v>
+      <c r="B53" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="54" spans="1:3" ht="30" hidden="1" x14ac:dyDescent="0.25">
@@ -1451,8 +1609,8 @@
       <c r="B54" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C54" s="4" t="s">
-        <v>81</v>
+      <c r="C54" s="3" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="55" spans="1:3" ht="75" hidden="1" x14ac:dyDescent="0.25">
@@ -1460,19 +1618,19 @@
         <v>35</v>
       </c>
       <c r="B55" s="1"/>
-      <c r="C55" s="4" t="s">
-        <v>81</v>
+      <c r="C55" s="3" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="56" spans="1:3" ht="30" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="B56" s="4" t="s">
+      <c r="A56" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="C56" s="4" t="s">
-        <v>81</v>
+      <c r="B56" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="57" spans="1:3" ht="240" hidden="1" x14ac:dyDescent="0.25">
@@ -1480,19 +1638,19 @@
         <v>22</v>
       </c>
       <c r="B57" s="1"/>
-      <c r="C57" s="4" t="s">
-        <v>81</v>
+      <c r="C57" s="3" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="58" spans="1:3" ht="60" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="4" t="s">
-        <v>119</v>
+      <c r="A58" s="3" t="s">
+        <v>118</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C58" s="4" t="s">
-        <v>81</v>
+      <c r="C58" s="3" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="59" spans="1:3" ht="30" hidden="1" x14ac:dyDescent="0.25">
@@ -1502,8 +1660,8 @@
       <c r="B59" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C59" s="4" t="s">
-        <v>111</v>
+      <c r="C59" s="3" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="60" spans="1:3" ht="45" hidden="1" x14ac:dyDescent="0.25">
@@ -1513,46 +1671,46 @@
       <c r="B60" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C60" s="4" t="s">
-        <v>81</v>
+      <c r="C60" s="3" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="61" spans="1:3" ht="105" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="4" t="s">
-        <v>121</v>
+      <c r="A61" s="3" t="s">
+        <v>120</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C61" s="4" t="s">
-        <v>88</v>
+      <c r="C61" s="3" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="62" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" s="1"/>
       <c r="B62" s="1"/>
-      <c r="C62" s="4" t="s">
-        <v>88</v>
+      <c r="C62" s="3" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="63" spans="1:3" ht="45" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="4" t="s">
-        <v>120</v>
+      <c r="A63" s="3" t="s">
+        <v>119</v>
       </c>
       <c r="B63" s="1"/>
-      <c r="C63" s="4" t="s">
-        <v>88</v>
+      <c r="C63" s="3" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="64" spans="1:3" ht="45" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="4" t="s">
+      <c r="A64" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="B64" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="B64" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="C64" s="4" t="s">
-        <v>81</v>
+      <c r="C64" s="3" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="65" spans="1:3" ht="30" hidden="1" x14ac:dyDescent="0.25">
@@ -1560,97 +1718,97 @@
         <v>46</v>
       </c>
       <c r="B65" s="1"/>
-      <c r="C65" s="4" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" ht="45" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="9" t="s">
+      <c r="C65" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" ht="45" x14ac:dyDescent="0.3">
+      <c r="A66" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="B66" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="B66" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="C66" s="4" t="s">
-        <v>154</v>
+      <c r="C66" s="3" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="67" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67"/>
       <c r="B67" s="1"/>
-      <c r="C67" s="4" t="s">
-        <v>81</v>
+      <c r="C67" s="3" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="68" spans="1:3" ht="30" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="4" t="s">
-        <v>124</v>
+      <c r="A68" s="3" t="s">
+        <v>123</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C68" s="4" t="s">
-        <v>81</v>
+      <c r="C68" s="3" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="69" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69"/>
       <c r="B69" s="1"/>
-      <c r="C69" s="4" t="s">
-        <v>81</v>
+      <c r="C69" s="3" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="70" spans="1:3" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B70" s="4" t="s">
+      <c r="B70" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" ht="30" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="C70" s="4" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" ht="30" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="4" t="s">
+      <c r="B71" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="B71" s="4" t="s">
+      <c r="C71" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" ht="30" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="3" t="s">
         <v>127</v>
-      </c>
-      <c r="C71" s="4" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3" ht="30" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="4" t="s">
-        <v>128</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C72" s="4" t="s">
-        <v>81</v>
+      <c r="C72" s="3" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="73" spans="1:3" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B73" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B73" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C73" s="4" t="s">
-        <v>81</v>
+      <c r="C73" s="3" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="74" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B74" s="1"/>
-      <c r="C74" s="4" t="s">
-        <v>81</v>
+      <c r="C74" s="3" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="75" spans="1:3" ht="30" hidden="1" x14ac:dyDescent="0.25">
@@ -1660,8 +1818,8 @@
       <c r="B75" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C75" s="4" t="s">
-        <v>81</v>
+      <c r="C75" s="3" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="76" spans="1:3" ht="45" hidden="1" x14ac:dyDescent="0.25">
@@ -1669,88 +1827,89 @@
         <v>23</v>
       </c>
       <c r="B76" s="1"/>
-      <c r="C76" s="4" t="s">
-        <v>81</v>
+      <c r="C76" s="3" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="77" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="4" t="s">
+      <c r="A77" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" ht="45" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="B77" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="C77" s="4" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3" ht="45" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="4" t="s">
+      <c r="B78" s="1"/>
+      <c r="C78" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="B78" s="1"/>
-      <c r="C78" s="4" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="4" t="s">
-        <v>132</v>
-      </c>
       <c r="B79" s="1"/>
-      <c r="C79" s="4" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="C79" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
+        <v>143</v>
+      </c>
+      <c r="B80" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="B80" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="C80" s="4" t="s">
-        <v>70</v>
+      <c r="C80" s="3" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="81" spans="1:3" ht="16.5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="5" t="s">
+      <c r="A81" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="B81" t="s">
+        <v>153</v>
+      </c>
+      <c r="C81" s="5" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" ht="16.5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A82" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="B82" t="s">
+        <v>154</v>
+      </c>
+      <c r="C82" s="5" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A83" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="B83" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="B81" t="s">
-        <v>159</v>
-      </c>
-      <c r="C81" s="6" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3" ht="16.5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="B82" t="s">
-        <v>160</v>
-      </c>
-      <c r="C82" s="6" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3" ht="30" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="8" t="s">
-        <v>163</v>
-      </c>
-      <c r="B83" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="C83" s="4" t="s">
-        <v>154</v>
+      <c r="C83" s="3" t="s">
+        <v>149</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:C83">
     <filterColumn colId="2">
       <filters>
-        <filter val="выезд"/>
+        <filter val="толщина"/>
+        <filter val="цена"/>
       </filters>
     </filterColumn>
   </autoFilter>

--- a/data/rag.xlsx
+++ b/data/rag.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="175">
   <si>
     <t>с чердака пенят паропроницаемой пеной толщиной 10 см и более</t>
   </si>
@@ -496,12 +496,6 @@
   </si>
   <si>
     <t>видео утепления мансарды из дерева</t>
-  </si>
-  <si>
-    <t>https://rutube.ru/video/1ea384edfe8f3e0fba2a104e7d45c492/</t>
-  </si>
-  <si>
-    <t>https://rutube.ru/video/258b4ddbe6081c4bb1785058c2b0ea57/</t>
   </si>
   <si>
     <t>видео</t>
@@ -665,6 +659,15 @@
   </si>
   <si>
     <t>цена утепления ППУ толщина 10 см  плотность 20 кг</t>
+  </si>
+  <si>
+    <t>видео утепления объект из материал</t>
+  </si>
+  <si>
+    <t>video-39043680_456239367</t>
+  </si>
+  <si>
+    <t>https://vkvideo.ru/video-39043680_456239468</t>
   </si>
 </sst>
 </file>
@@ -1041,7 +1044,7 @@
         <v>65</v>
       </c>
       <c r="D1" s="12" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="2" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
@@ -1066,9 +1069,9 @@
         <v>66</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>145</v>
@@ -1077,12 +1080,12 @@
         <v>136</v>
       </c>
       <c r="D4" s="9" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
         <v>167</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
-        <v>169</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>146</v>
@@ -1091,9 +1094,9 @@
         <v>136</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>147</v>
@@ -1102,9 +1105,9 @@
         <v>136</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>148</v>
@@ -1137,7 +1140,7 @@
     </row>
     <row r="10" spans="1:4" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>3</v>
@@ -1157,9 +1160,9 @@
         <v>70</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>150</v>
@@ -1168,7 +1171,7 @@
         <v>149</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="45" hidden="1" x14ac:dyDescent="0.25">
@@ -1182,12 +1185,12 @@
         <v>68</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>149</v>
@@ -1447,12 +1450,12 @@
         <v>99</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="6" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>149</v>
@@ -1533,7 +1536,7 @@
     </row>
     <row r="47" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B47" s="1"/>
       <c r="C47" s="3" t="s">
@@ -1591,12 +1594,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="53" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
         <v>115</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C53" s="3" t="s">
         <v>149</v>
@@ -1722,12 +1725,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="66" spans="1:3" ht="45" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:3" ht="45" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" s="7" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C66" s="3" t="s">
         <v>149</v>
@@ -1871,34 +1874,37 @@
         <v>69</v>
       </c>
     </row>
-    <row r="81" spans="1:3" ht="16.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A81" s="4" t="s">
         <v>151</v>
       </c>
       <c r="B81" t="s">
+        <v>173</v>
+      </c>
+      <c r="C81" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="C81" s="5" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3" ht="16.5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="D81" s="4" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A82" s="4" t="s">
         <v>152</v>
       </c>
       <c r="B82" t="s">
-        <v>154</v>
+        <v>174</v>
       </c>
       <c r="C82" s="5" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A83" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="B83" s="3" t="s">
         <v>155</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A83" s="6" t="s">
-        <v>165</v>
-      </c>
-      <c r="B83" s="3" t="s">
-        <v>157</v>
       </c>
       <c r="C83" s="3" t="s">
         <v>149</v>
@@ -1908,8 +1914,7 @@
   <autoFilter ref="A1:C83">
     <filterColumn colId="2">
       <filters>
-        <filter val="толщина"/>
-        <filter val="цена"/>
+        <filter val="видео"/>
       </filters>
     </filterColumn>
   </autoFilter>
